--- a/Aula_Play.xlsx
+++ b/Aula_Play.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diana Fonseca\Documentos Oficiales\BI - Proyectos\1. Proyectos Phyton\Inmersion 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B0D118-F595-4C4B-AD77-288A254620B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751D9EE6-DFE1-439E-BA19-6F891D99554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>https://script.google.com/macros/s/AKfycbya8g3HQXtWdm5owELADAdtU3eHdGQJKyc4mbG8d8owNSkV-AxjX88cx3WeBxYay_zn-Q/exec</t>
+    <t>https://script.google.com/macros/s/AKfycby7cZMseSBRD_PGMi2kNlRm-t1n9IfM2IqVpTKtNkw-8rt1R2EoBWoXDa4-aQ_1htM8qQ/exec</t>
   </si>
 </sst>
 </file>
@@ -366,7 +366,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{1959205C-2CF4-4D03-9373-AD32A1EBCAC3}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{C23865CD-FB49-440E-8090-1609EE2DFF60}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Aula_Play.xlsx
+++ b/Aula_Play.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diana Fonseca\Documentos Oficiales\BI - Proyectos\1. Proyectos Phyton\Inmersion 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751D9EE6-DFE1-439E-BA19-6F891D99554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C41F37-C6F2-4182-B4C6-62C4E0934D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,7 +366,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{C23865CD-FB49-440E-8090-1609EE2DFF60}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{B759C687-4578-4E24-BF79-A3B351E399D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Aula_Play.xlsx
+++ b/Aula_Play.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diana Fonseca\Documentos Oficiales\BI - Proyectos\1. Proyectos Phyton\Inmersion 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C41F37-C6F2-4182-B4C6-62C4E0934D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8C200B-F989-46D6-918E-CB3942C64A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,7 +366,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{B759C687-4578-4E24-BF79-A3B351E399D7}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{60452B4B-64C6-436B-85E6-A50F138EA575}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
